--- a/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
@@ -1,22 +1,291 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5519531C-6A14-4E26-8343-56C82D85B66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Blue_Shark_NPac</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>6.784</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.146</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.639</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>245.2</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.992</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.496</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.903</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.735</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.032</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.624</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.997</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +333,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +385,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +419,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +454,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +630,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="43.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Blue_Shark_NPac</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6.784</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.639</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.992</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.496</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.903</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.735</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.032</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.624</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.997</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.597</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.638</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.708</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.941</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1000,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1971</v>
       </c>
@@ -1148,7 +1089,7 @@
         <v>35800</v>
       </c>
       <c r="G2">
-        <v>1.773</v>
+        <v>1.7729999999999999</v>
       </c>
       <c r="H2">
         <v>440</v>
@@ -1160,7 +1101,7 @@
         <v>35355</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1972</v>
       </c>
@@ -1180,12 +1121,12 @@
         <v>33064</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1973</v>
       </c>
       <c r="B4">
-        <v>34991.8</v>
+        <v>34991.800000000003</v>
       </c>
       <c r="G4">
         <v>1.276</v>
@@ -1197,15 +1138,15 @@
         <v>1</v>
       </c>
       <c r="T4">
-        <v>34550.8</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>34550.800000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1974</v>
       </c>
       <c r="B5">
-        <v>31292.8</v>
+        <v>31292.799999999999</v>
       </c>
       <c r="G5">
         <v>1.278</v>
@@ -1217,15 +1158,15 @@
         <v>134</v>
       </c>
       <c r="T5">
-        <v>30718.8</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>30718.799999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1975</v>
       </c>
       <c r="B6">
-        <v>37346.7</v>
+        <v>37346.699999999997</v>
       </c>
       <c r="G6">
         <v>1.284</v>
@@ -1237,10 +1178,10 @@
         <v>200</v>
       </c>
       <c r="T6">
-        <v>36706.7</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>36706.699999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1976</v>
       </c>
@@ -1248,7 +1189,7 @@
         <v>53884.9</v>
       </c>
       <c r="G7">
-        <v>1.289</v>
+        <v>1.2889999999999999</v>
       </c>
       <c r="H7">
         <v>374</v>
@@ -1263,7 +1204,7 @@
         <v>1.341</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1977</v>
       </c>
@@ -1271,7 +1212,7 @@
         <v>69949</v>
       </c>
       <c r="G8">
-        <v>1.297</v>
+        <v>1.2969999999999999</v>
       </c>
       <c r="H8">
         <v>386</v>
@@ -1286,7 +1227,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1978</v>
       </c>
@@ -1309,12 +1250,12 @@
         <v>1.202</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1979</v>
       </c>
       <c r="B10">
-        <v>68432.39999999999</v>
+        <v>68432.399999999994</v>
       </c>
       <c r="C10">
         <v>114.185</v>
@@ -1323,7 +1264,7 @@
         <v>0.309</v>
       </c>
       <c r="F10">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="G10">
         <v>1.276</v>
@@ -1335,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="T10">
-        <v>68080.39999999999</v>
+        <v>68080.399999999994</v>
       </c>
       <c r="U10">
         <v>114.185</v>
@@ -1344,13 +1285,13 @@
         <v>0.309</v>
       </c>
       <c r="X10">
-        <v>0.096</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="Y10">
-        <v>1.261</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1.2609999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1980</v>
       </c>
@@ -1361,13 +1302,13 @@
         <v>106.759</v>
       </c>
       <c r="E11">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="F11">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G11">
-        <v>1.237</v>
+        <v>1.2370000000000001</v>
       </c>
       <c r="H11">
         <v>336</v>
@@ -1382,16 +1323,16 @@
         <v>106.759</v>
       </c>
       <c r="W11">
-        <v>0.282</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="X11">
-        <v>0.045</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Y11">
         <v>1.351</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1981</v>
       </c>
@@ -1399,16 +1340,16 @@
         <v>69958</v>
       </c>
       <c r="C12">
-        <v>132.207</v>
+        <v>132.20699999999999</v>
       </c>
       <c r="E12">
-        <v>0.327</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="F12">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G12">
-        <v>1.207</v>
+        <v>1.2070000000000001</v>
       </c>
       <c r="H12">
         <v>256</v>
@@ -1420,19 +1361,19 @@
         <v>69662</v>
       </c>
       <c r="U12">
-        <v>132.207</v>
+        <v>132.20699999999999</v>
       </c>
       <c r="W12">
-        <v>0.327</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="X12">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="Y12">
-        <v>1.122</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>1.1220000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1982</v>
       </c>
@@ -1446,7 +1387,7 @@
         <v>0.23</v>
       </c>
       <c r="F13">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="G13">
         <v>1.17</v>
@@ -1467,13 +1408,13 @@
         <v>0.23</v>
       </c>
       <c r="X13">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="Y13">
-        <v>1.102</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>1.1020000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1983</v>
       </c>
@@ -1481,16 +1422,16 @@
         <v>52017.4</v>
       </c>
       <c r="C14">
-        <v>153.182</v>
+        <v>153.18199999999999</v>
       </c>
       <c r="E14">
         <v>0.218</v>
       </c>
       <c r="F14">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="G14">
-        <v>1.134</v>
+        <v>1.1339999999999999</v>
       </c>
       <c r="H14">
         <v>293</v>
@@ -1502,19 +1443,19 @@
         <v>51719.4</v>
       </c>
       <c r="U14">
-        <v>153.182</v>
+        <v>153.18199999999999</v>
       </c>
       <c r="W14">
         <v>0.218</v>
       </c>
       <c r="X14">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="Y14">
-        <v>1.043</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>1.0429999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1984</v>
       </c>
@@ -1534,10 +1475,10 @@
         <v>49578.3</v>
       </c>
       <c r="Y15">
-        <v>0.904</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>0.90400000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1985</v>
       </c>
@@ -1557,10 +1498,10 @@
         <v>48066.5</v>
       </c>
       <c r="Y16">
-        <v>0.775</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1986</v>
       </c>
@@ -1568,7 +1509,7 @@
         <v>43161.1</v>
       </c>
       <c r="G17">
-        <v>1.051</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="H17">
         <v>407</v>
@@ -1580,18 +1521,18 @@
         <v>42616.1</v>
       </c>
       <c r="Y17">
-        <v>0.904</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>0.90400000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1987</v>
       </c>
       <c r="B18">
-        <v>36421.6</v>
+        <v>36421.599999999999</v>
       </c>
       <c r="G18">
-        <v>1.011</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="H18">
         <v>351</v>
@@ -1603,18 +1544,18 @@
         <v>36014.6</v>
       </c>
       <c r="Y18">
-        <v>0.675</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1988</v>
       </c>
       <c r="B19">
-        <v>40902.3</v>
+        <v>40902.300000000003</v>
       </c>
       <c r="G19">
-        <v>0.956</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="H19">
         <v>509</v>
@@ -1623,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>40383.3</v>
+        <v>40383.300000000003</v>
       </c>
       <c r="Y19">
-        <v>0.705</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>0.70499999999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1989</v>
       </c>
@@ -1637,7 +1578,7 @@
         <v>42514</v>
       </c>
       <c r="G20">
-        <v>0.902</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="H20">
         <v>280</v>
@@ -1649,10 +1590,10 @@
         <v>42180</v>
       </c>
       <c r="Y20">
-        <v>0.636</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>0.63600000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1990</v>
       </c>
@@ -1663,13 +1604,13 @@
         <v>118.81</v>
       </c>
       <c r="E21">
-        <v>0.258</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="F21">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="G21">
-        <v>0.851</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="H21">
         <v>1130</v>
@@ -1684,16 +1625,16 @@
         <v>118.81</v>
       </c>
       <c r="W21">
-        <v>0.258</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="X21">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="Y21">
-        <v>0.665</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>0.66500000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1991</v>
       </c>
@@ -1701,16 +1642,16 @@
         <v>37515.9</v>
       </c>
       <c r="C22">
-        <v>133.889</v>
+        <v>133.88900000000001</v>
       </c>
       <c r="E22">
         <v>0.37</v>
       </c>
       <c r="F22">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="G22">
-        <v>0.791</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="H22">
         <v>1016</v>
@@ -1722,19 +1663,19 @@
         <v>36269.9</v>
       </c>
       <c r="U22">
-        <v>133.889</v>
+        <v>133.88900000000001</v>
       </c>
       <c r="W22">
         <v>0.37</v>
       </c>
       <c r="X22">
-        <v>0.333</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="Y22">
-        <v>0.844</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>0.84399999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1992</v>
       </c>
@@ -1742,16 +1683,16 @@
         <v>33307.9</v>
       </c>
       <c r="C23">
-        <v>133.794</v>
+        <v>133.79400000000001</v>
       </c>
       <c r="E23">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="F23">
-        <v>0.346</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="G23">
-        <v>0.733</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="H23">
         <v>1636</v>
@@ -1763,19 +1704,19 @@
         <v>31596.9</v>
       </c>
       <c r="U23">
-        <v>133.794</v>
+        <v>133.79400000000001</v>
       </c>
       <c r="W23">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="X23">
-        <v>0.346</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="Y23">
-        <v>0.884</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -1813,10 +1754,10 @@
         <v>0.24</v>
       </c>
       <c r="Y24">
-        <v>0.963</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>0.96299999999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1994</v>
       </c>
@@ -1827,13 +1768,13 @@
         <v>124.883</v>
       </c>
       <c r="E25">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="F25">
         <v>0.23</v>
       </c>
       <c r="G25">
-        <v>0.6909999999999999</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="H25">
         <v>1758</v>
@@ -1842,22 +1783,22 @@
         <v>12</v>
       </c>
       <c r="T25">
-        <v>41696.7</v>
+        <v>41696.699999999997</v>
       </c>
       <c r="U25">
         <v>124.883</v>
       </c>
       <c r="W25">
-        <v>0.266</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="X25">
         <v>0.23</v>
       </c>
       <c r="Y25">
-        <v>1.118</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>1.1180000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1995</v>
       </c>
@@ -1865,16 +1806,16 @@
         <v>47454.6</v>
       </c>
       <c r="C26">
-        <v>140.879</v>
+        <v>140.87899999999999</v>
       </c>
       <c r="E26">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="F26">
         <v>0.376</v>
       </c>
       <c r="G26">
-        <v>0.704</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="H26">
         <v>2100</v>
@@ -1886,10 +1827,10 @@
         <v>44716.6</v>
       </c>
       <c r="U26">
-        <v>140.879</v>
+        <v>140.87899999999999</v>
       </c>
       <c r="W26">
-        <v>0.173</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="X26">
         <v>0.376</v>
@@ -1898,7 +1839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1996</v>
       </c>
@@ -1909,13 +1850,13 @@
         <v>129.017</v>
       </c>
       <c r="E27">
-        <v>0.194</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="F27">
-        <v>0.226</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="G27">
-        <v>0.719</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="H27">
         <v>3117</v>
@@ -1924,22 +1865,22 @@
         <v>275</v>
       </c>
       <c r="T27">
-        <v>38736.2</v>
+        <v>38736.199999999997</v>
       </c>
       <c r="U27">
         <v>129.017</v>
       </c>
       <c r="W27">
-        <v>0.194</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="X27">
-        <v>0.226</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="Y27">
         <v>1.075</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1997</v>
       </c>
@@ -1947,16 +1888,16 @@
         <v>47922.7</v>
       </c>
       <c r="C28">
-        <v>135.954</v>
+        <v>135.95400000000001</v>
       </c>
       <c r="E28">
         <v>0.224</v>
       </c>
       <c r="F28">
-        <v>0.292</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="G28">
-        <v>0.734</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="H28">
         <v>2948</v>
@@ -1968,19 +1909,19 @@
         <v>44654.7</v>
       </c>
       <c r="U28">
-        <v>135.954</v>
+        <v>135.95400000000001</v>
       </c>
       <c r="W28">
         <v>0.224</v>
       </c>
       <c r="X28">
-        <v>0.292</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="Y28">
-        <v>1.213</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>1.2130000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1998</v>
       </c>
@@ -1988,16 +1929,16 @@
         <v>46291.9</v>
       </c>
       <c r="C29">
-        <v>132.152</v>
+        <v>132.15199999999999</v>
       </c>
       <c r="E29">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F29">
-        <v>0.269</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="G29">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H29">
         <v>3134</v>
@@ -2009,19 +1950,19 @@
         <v>42820.9</v>
       </c>
       <c r="U29">
-        <v>132.152</v>
+        <v>132.15199999999999</v>
       </c>
       <c r="W29">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="X29">
-        <v>0.269</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="Y29">
         <v>1.349</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1999</v>
       </c>
@@ -2029,16 +1970,16 @@
         <v>51535.4</v>
       </c>
       <c r="C30">
-        <v>136.632</v>
+        <v>136.63200000000001</v>
       </c>
       <c r="E30">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F30">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="G30">
-        <v>0.767</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="H30">
         <v>2261</v>
@@ -2050,19 +1991,19 @@
         <v>48651.4</v>
       </c>
       <c r="U30">
-        <v>136.632</v>
+        <v>136.63200000000001</v>
       </c>
       <c r="W30">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="X30">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="Y30">
-        <v>1.299</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>1.2989999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -2070,16 +2011,16 @@
         <v>55109.2</v>
       </c>
       <c r="C31">
-        <v>144.051</v>
+        <v>144.05099999999999</v>
       </c>
       <c r="E31">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="F31">
-        <v>0.418</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="G31">
-        <v>0.798</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="H31">
         <v>2719</v>
@@ -2091,19 +2032,19 @@
         <v>51706.2</v>
       </c>
       <c r="U31">
-        <v>144.051</v>
+        <v>144.05099999999999</v>
       </c>
       <c r="W31">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="X31">
-        <v>0.418</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="Y31">
-        <v>1.192</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>1.1919999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2001</v>
       </c>
@@ -2120,7 +2061,7 @@
         <v>0.375</v>
       </c>
       <c r="G32">
-        <v>0.842</v>
+        <v>0.84199999999999997</v>
       </c>
       <c r="H32">
         <v>2587</v>
@@ -2144,7 +2085,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2002</v>
       </c>
@@ -2152,13 +2093,13 @@
         <v>44311</v>
       </c>
       <c r="C33">
-        <v>142.819</v>
+        <v>142.81899999999999</v>
       </c>
       <c r="E33">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F33">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="G33">
         <v>0.88</v>
@@ -2173,36 +2114,36 @@
         <v>40430</v>
       </c>
       <c r="U33">
-        <v>142.819</v>
+        <v>142.81899999999999</v>
       </c>
       <c r="W33">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="X33">
-        <v>0.409</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="Y33">
         <v>1.052</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2003</v>
       </c>
       <c r="B34">
-        <v>40435.3</v>
+        <v>40435.300000000003</v>
       </c>
       <c r="C34">
         <v>141.6</v>
       </c>
       <c r="E34">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="F34">
-        <v>0.359</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="G34">
-        <v>0.906</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="H34">
         <v>2307</v>
@@ -2211,22 +2152,22 @@
         <v>777</v>
       </c>
       <c r="T34">
-        <v>37351.3</v>
+        <v>37351.300000000003</v>
       </c>
       <c r="U34">
         <v>141.6</v>
       </c>
       <c r="W34">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="X34">
-        <v>0.359</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="Y34">
         <v>1.087</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2004</v>
       </c>
@@ -2240,10 +2181,10 @@
         <v>0.217</v>
       </c>
       <c r="F35">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="G35">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="H35">
         <v>3781</v>
@@ -2252,19 +2193,19 @@
         <v>1189</v>
       </c>
       <c r="O35">
-        <v>179.062</v>
+        <v>179.06200000000001</v>
       </c>
       <c r="Q35">
-        <v>0.201</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="R35">
-        <v>0.8120000000000001</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="S35">
         <v>0.24</v>
       </c>
       <c r="T35">
-        <v>37744.3</v>
+        <v>37744.300000000003</v>
       </c>
       <c r="U35">
         <v>140.94</v>
@@ -2273,13 +2214,13 @@
         <v>0.219</v>
       </c>
       <c r="X35">
-        <v>0.335</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="Y35">
-        <v>1.064</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>1.0640000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2005</v>
       </c>
@@ -2287,7 +2228,7 @@
         <v>43812.3</v>
       </c>
       <c r="C36">
-        <v>156.718</v>
+        <v>156.71799999999999</v>
       </c>
       <c r="E36">
         <v>0.224</v>
@@ -2296,7 +2237,7 @@
         <v>0.5</v>
       </c>
       <c r="G36">
-        <v>0.958</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="H36">
         <v>2721</v>
@@ -2305,25 +2246,25 @@
         <v>915</v>
       </c>
       <c r="O36">
-        <v>208.026</v>
+        <v>208.02600000000001</v>
       </c>
       <c r="Q36">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="R36">
-        <v>0.868</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="S36">
         <v>1.4</v>
       </c>
       <c r="T36">
-        <v>40176.3</v>
+        <v>40176.300000000003</v>
       </c>
       <c r="U36">
         <v>148.167</v>
       </c>
       <c r="W36">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="X36">
         <v>0.439</v>
@@ -2332,12 +2273,12 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2006</v>
       </c>
       <c r="B37">
-        <v>40258.3</v>
+        <v>40258.300000000003</v>
       </c>
       <c r="C37">
         <v>154.738</v>
@@ -2346,22 +2287,22 @@
         <v>0.222</v>
       </c>
       <c r="F37">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="G37">
-        <v>0.978</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H37">
         <v>2765</v>
       </c>
       <c r="I37">
-        <v>130.764</v>
+        <v>130.76400000000001</v>
       </c>
       <c r="K37">
         <v>0.248</v>
       </c>
       <c r="L37">
-        <v>0.199</v>
+        <v>0.19900000000000001</v>
       </c>
       <c r="M37">
         <v>1.321</v>
@@ -2370,34 +2311,34 @@
         <v>884</v>
       </c>
       <c r="O37">
-        <v>194.367</v>
+        <v>194.36699999999999</v>
       </c>
       <c r="Q37">
         <v>0.219</v>
       </c>
       <c r="R37">
-        <v>0.848</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="S37">
         <v>0.8</v>
       </c>
       <c r="T37">
-        <v>36609.3</v>
+        <v>36609.300000000003</v>
       </c>
       <c r="U37">
-        <v>152.129</v>
+        <v>152.12899999999999</v>
       </c>
       <c r="W37">
         <v>0.219</v>
       </c>
       <c r="X37">
-        <v>0.459</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="Y37">
         <v>0.877</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -2405,25 +2346,25 @@
         <v>38605.4</v>
       </c>
       <c r="C38">
-        <v>152.371</v>
+        <v>152.37100000000001</v>
       </c>
       <c r="E38">
-        <v>0.236</v>
+        <v>0.23599999999999999</v>
       </c>
       <c r="F38">
         <v>0.435</v>
       </c>
       <c r="G38">
-        <v>0.991</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="H38">
         <v>3324</v>
       </c>
       <c r="I38">
-        <v>135.091</v>
+        <v>135.09100000000001</v>
       </c>
       <c r="K38">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="L38">
         <v>0.249</v>
@@ -2435,13 +2376,13 @@
         <v>818</v>
       </c>
       <c r="O38">
-        <v>188.171</v>
+        <v>188.17099999999999</v>
       </c>
       <c r="Q38">
         <v>0.248</v>
       </c>
       <c r="R38">
-        <v>0.732</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="S38">
         <v>0.51</v>
@@ -2453,16 +2394,16 @@
         <v>149.285</v>
       </c>
       <c r="W38">
-        <v>0.233</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="X38">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="Y38">
-        <v>0.8080000000000001</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>0.80800000000000005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2008</v>
       </c>
@@ -2470,16 +2411,16 @@
         <v>36373</v>
       </c>
       <c r="C39">
-        <v>148.23</v>
+        <v>148.22999999999999</v>
       </c>
       <c r="E39">
         <v>0.23</v>
       </c>
       <c r="F39">
-        <v>0.414</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="G39">
-        <v>0.994</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="H39">
         <v>4355</v>
@@ -2488,46 +2429,46 @@
         <v>140.279</v>
       </c>
       <c r="K39">
-        <v>0.201</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="L39">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="M39">
-        <v>1.261</v>
+        <v>1.2609999999999999</v>
       </c>
       <c r="N39">
         <v>680</v>
       </c>
       <c r="O39">
-        <v>204.074</v>
+        <v>204.07400000000001</v>
       </c>
       <c r="Q39">
         <v>0.183</v>
       </c>
       <c r="R39">
-        <v>0.907</v>
+        <v>0.90700000000000003</v>
       </c>
       <c r="S39">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="T39">
         <v>31338</v>
       </c>
       <c r="U39">
-        <v>141.388</v>
+        <v>141.38800000000001</v>
       </c>
       <c r="W39">
-        <v>0.241</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="X39">
-        <v>0.368</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="Y39">
         <v>0.623</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2009</v>
       </c>
@@ -2544,69 +2485,69 @@
         <v>0.434</v>
       </c>
       <c r="G40">
-        <v>0.985</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="H40">
         <v>4423</v>
       </c>
       <c r="I40">
-        <v>143.265</v>
+        <v>143.26499999999999</v>
       </c>
       <c r="K40">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="L40">
-        <v>0.241</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="M40">
-        <v>0.991</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="N40">
         <v>478</v>
       </c>
       <c r="O40">
-        <v>191.757</v>
+        <v>191.75700000000001</v>
       </c>
       <c r="Q40">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="R40">
-        <v>0.784</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="S40">
         <v>0.41</v>
       </c>
       <c r="T40">
-        <v>34101.6</v>
+        <v>34101.599999999999</v>
       </c>
       <c r="U40">
-        <v>146.432</v>
+        <v>146.43199999999999</v>
       </c>
       <c r="W40">
-        <v>0.269</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="X40">
-        <v>0.408</v>
+        <v>0.40799999999999997</v>
       </c>
       <c r="Y40">
-        <v>0.714</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>0.71399999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2010</v>
       </c>
       <c r="B41">
-        <v>36524.3</v>
+        <v>36524.300000000003</v>
       </c>
       <c r="C41">
-        <v>147.526</v>
+        <v>147.52600000000001</v>
       </c>
       <c r="E41">
-        <v>0.243</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="F41">
-        <v>0.404</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="G41">
         <v>0.96</v>
@@ -2615,25 +2556,25 @@
         <v>4469</v>
       </c>
       <c r="I41">
-        <v>146.348</v>
+        <v>146.34800000000001</v>
       </c>
       <c r="K41">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="L41">
         <v>0.316</v>
       </c>
       <c r="M41">
-        <v>0.831</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="N41">
         <v>334</v>
       </c>
       <c r="O41">
-        <v>181.556</v>
+        <v>181.55600000000001</v>
       </c>
       <c r="Q41">
-        <v>0.146</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="R41">
         <v>0.8</v>
@@ -2645,19 +2586,19 @@
         <v>31721.3</v>
       </c>
       <c r="U41">
-        <v>140.956</v>
+        <v>140.95599999999999</v>
       </c>
       <c r="W41">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="X41">
-        <v>0.342</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="Y41">
         <v>0.87</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2011</v>
       </c>
@@ -2665,64 +2606,64 @@
         <v>31164.6</v>
       </c>
       <c r="C42">
-        <v>146.082</v>
+        <v>146.08199999999999</v>
       </c>
       <c r="E42">
-        <v>0.234</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F42">
-        <v>0.406</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="G42">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="H42">
         <v>3719</v>
       </c>
       <c r="I42">
-        <v>139.528</v>
+        <v>139.52799999999999</v>
       </c>
       <c r="K42">
-        <v>0.257</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="L42">
-        <v>0.294</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="M42">
-        <v>0.761</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="N42">
         <v>594</v>
       </c>
       <c r="O42">
-        <v>189.868</v>
+        <v>189.86799999999999</v>
       </c>
       <c r="Q42">
         <v>0.127</v>
       </c>
       <c r="R42">
-        <v>0.895</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="S42">
         <v>0.74</v>
       </c>
       <c r="T42">
-        <v>26851.6</v>
+        <v>26851.599999999999</v>
       </c>
       <c r="U42">
-        <v>140.763</v>
+        <v>140.76300000000001</v>
       </c>
       <c r="W42">
         <v>0.246</v>
       </c>
       <c r="X42">
-        <v>0.352</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="Y42">
-        <v>0.798</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>0.79800000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2012</v>
       </c>
@@ -2730,22 +2671,22 @@
         <v>33863</v>
       </c>
       <c r="C43">
-        <v>146.062</v>
+        <v>146.06200000000001</v>
       </c>
       <c r="E43">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="F43">
-        <v>0.397</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="G43">
-        <v>0.923</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="H43">
         <v>4108</v>
       </c>
       <c r="I43">
-        <v>134.837</v>
+        <v>134.83699999999999</v>
       </c>
       <c r="K43">
         <v>0.189</v>
@@ -2754,7 +2695,7 @@
         <v>0.17</v>
       </c>
       <c r="M43">
-        <v>1.231</v>
+        <v>1.2310000000000001</v>
       </c>
       <c r="N43">
         <v>594</v>
@@ -2763,7 +2704,7 @@
         <v>173.774</v>
       </c>
       <c r="Q43">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="R43">
         <v>0.66</v>
@@ -2775,19 +2716,19 @@
         <v>29161</v>
       </c>
       <c r="U43">
-        <v>144.23</v>
+        <v>144.22999999999999</v>
       </c>
       <c r="W43">
         <v>0.216</v>
       </c>
       <c r="X43">
-        <v>0.393</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="Y43">
         <v>0.752</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2013</v>
       </c>
@@ -2795,46 +2736,46 @@
         <v>26212.7</v>
       </c>
       <c r="C44">
-        <v>153.713</v>
+        <v>153.71299999999999</v>
       </c>
       <c r="E44">
         <v>0.224</v>
       </c>
       <c r="F44">
-        <v>0.474</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="G44">
-        <v>0.917</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="H44">
         <v>4494</v>
       </c>
       <c r="I44">
-        <v>137.907</v>
+        <v>137.90700000000001</v>
       </c>
       <c r="K44">
         <v>0.182</v>
       </c>
       <c r="L44">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="M44">
-        <v>1.281</v>
+        <v>1.2809999999999999</v>
       </c>
       <c r="N44">
         <v>551</v>
       </c>
       <c r="O44">
-        <v>168.689</v>
+        <v>168.68899999999999</v>
       </c>
       <c r="Q44">
         <v>0.15</v>
       </c>
       <c r="R44">
-        <v>0.738</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="S44">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="T44">
         <v>21167.7</v>
@@ -2843,16 +2784,16 @@
         <v>153.816</v>
       </c>
       <c r="W44">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="X44">
-        <v>0.477</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="Y44">
-        <v>0.838</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2014</v>
       </c>
@@ -2866,22 +2807,22 @@
         <v>0.21</v>
       </c>
       <c r="F45">
-        <v>0.407</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="G45">
-        <v>0.913</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="H45">
         <v>5502</v>
       </c>
       <c r="I45">
-        <v>136.146</v>
+        <v>136.14599999999999</v>
       </c>
       <c r="K45">
         <v>0.185</v>
       </c>
       <c r="L45">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="M45">
         <v>1.101</v>
@@ -2893,10 +2834,10 @@
         <v>176.714</v>
       </c>
       <c r="Q45">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="R45">
-        <v>0.771</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="S45">
         <v>0.7</v>
@@ -2905,7 +2846,7 @@
         <v>25388.5</v>
       </c>
       <c r="U45">
-        <v>146.681</v>
+        <v>146.68100000000001</v>
       </c>
       <c r="W45">
         <v>0.221</v>
@@ -2914,10 +2855,10 @@
         <v>0.39</v>
       </c>
       <c r="Y45">
-        <v>1.003</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>1.0029999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2015</v>
       </c>
@@ -2925,28 +2866,28 @@
         <v>26372.3</v>
       </c>
       <c r="C46">
-        <v>154.337</v>
+        <v>154.33699999999999</v>
       </c>
       <c r="F46">
-        <v>0.477</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="G46">
-        <v>0.907</v>
+        <v>0.90700000000000003</v>
       </c>
       <c r="H46">
         <v>3985</v>
       </c>
       <c r="I46">
-        <v>138.615</v>
+        <v>138.61500000000001</v>
       </c>
       <c r="K46">
-        <v>0.162</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="L46">
         <v>0.159</v>
       </c>
       <c r="M46">
-        <v>0.781</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="N46">
         <v>1186</v>
@@ -2958,7 +2899,7 @@
         <v>0.192</v>
       </c>
       <c r="R46">
-        <v>0.798</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="S46">
         <v>1.59</v>
@@ -2967,16 +2908,16 @@
         <v>21201.3</v>
       </c>
       <c r="U46">
-        <v>150.757</v>
+        <v>150.75700000000001</v>
       </c>
       <c r="X46">
-        <v>0.476</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="Y46">
         <v>1.01</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2016</v>
       </c>
@@ -2987,13 +2928,13 @@
         <v>157.989</v>
       </c>
       <c r="E47">
-        <v>0.195</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="F47">
-        <v>0.509</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="G47">
-        <v>0.916</v>
+        <v>0.91600000000000004</v>
       </c>
       <c r="H47">
         <v>4973</v>
@@ -3002,37 +2943,37 @@
         <v>145.745</v>
       </c>
       <c r="K47">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="L47">
-        <v>0.338</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="M47">
-        <v>1.051</v>
+        <v>1.0509999999999999</v>
       </c>
       <c r="N47">
         <v>430</v>
       </c>
       <c r="O47">
-        <v>199.945</v>
+        <v>199.94499999999999</v>
       </c>
       <c r="Q47">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="R47">
-        <v>0.791</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="S47">
         <v>1.21</v>
       </c>
       <c r="T47">
-        <v>23775.6</v>
+        <v>23775.599999999999</v>
       </c>
       <c r="U47">
         <v>155.017</v>
       </c>
       <c r="W47">
-        <v>0.197</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="X47">
         <v>0.498</v>
@@ -3041,7 +2982,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2017</v>
       </c>
@@ -3052,13 +2993,13 @@
         <v>148.298</v>
       </c>
       <c r="E48">
-        <v>0.205</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="F48">
-        <v>0.417</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="G48">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="H48">
         <v>3384</v>
@@ -3067,10 +3008,10 @@
         <v>147.797</v>
       </c>
       <c r="K48">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="L48">
-        <v>0.332</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="M48">
         <v>0.74</v>
@@ -3079,19 +3020,19 @@
         <v>367</v>
       </c>
       <c r="O48">
-        <v>155.895</v>
+        <v>155.89500000000001</v>
       </c>
       <c r="Q48">
         <v>0.121</v>
       </c>
       <c r="R48">
-        <v>0.453</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="S48">
         <v>1.55</v>
       </c>
       <c r="T48">
-        <v>24646.4</v>
+        <v>24646.400000000001</v>
       </c>
       <c r="U48">
         <v>147.51</v>
@@ -3100,13 +3041,13 @@
         <v>0.218</v>
       </c>
       <c r="X48">
-        <v>0.422</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="Y48">
-        <v>1.106</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>1.1060000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2018</v>
       </c>
@@ -3120,25 +3061,25 @@
         <v>0.192</v>
       </c>
       <c r="F49">
-        <v>0.493</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="G49">
-        <v>0.974</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="H49">
         <v>2852</v>
       </c>
       <c r="I49">
-        <v>153.591</v>
+        <v>153.59100000000001</v>
       </c>
       <c r="K49">
-        <v>0.142</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="L49">
-        <v>0.366</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="M49">
-        <v>0.911</v>
+        <v>0.91100000000000003</v>
       </c>
       <c r="N49">
         <v>402</v>
@@ -3147,10 +3088,10 @@
         <v>167.125</v>
       </c>
       <c r="Q49">
-        <v>0.137</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="R49">
-        <v>0.675</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="S49">
         <v>1.22</v>
@@ -3162,16 +3103,16 @@
         <v>153.107</v>
       </c>
       <c r="W49">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="X49">
-        <v>0.487</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="Y49">
-        <v>1.045</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>1.0449999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -3185,7 +3126,7 @@
         <v>0.185</v>
       </c>
       <c r="F50">
-        <v>0.494</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G50">
         <v>1.006</v>
@@ -3197,10 +3138,10 @@
         <v>154.19</v>
       </c>
       <c r="K50">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="L50">
-        <v>0.533</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="M50">
         <v>1.101</v>
@@ -3209,13 +3150,13 @@
         <v>1298</v>
       </c>
       <c r="O50">
-        <v>192.308</v>
+        <v>192.30799999999999</v>
       </c>
       <c r="Q50">
-        <v>0.132</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="R50">
-        <v>0.923</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="S50">
         <v>1.46</v>
@@ -3224,19 +3165,19 @@
         <v>26927.5</v>
       </c>
       <c r="U50">
-        <v>148.436</v>
+        <v>148.43600000000001</v>
       </c>
       <c r="W50">
         <v>0.188</v>
       </c>
       <c r="X50">
-        <v>0.447</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="Y50">
         <v>1.044</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -3244,28 +3185,28 @@
         <v>26713.4</v>
       </c>
       <c r="C51">
-        <v>146.373</v>
+        <v>146.37299999999999</v>
       </c>
       <c r="F51">
-        <v>0.449</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="G51">
-        <v>1.023</v>
+        <v>1.0229999999999999</v>
       </c>
       <c r="H51">
         <v>3533</v>
       </c>
       <c r="I51">
-        <v>156.407</v>
+        <v>156.40700000000001</v>
       </c>
       <c r="K51">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="L51">
-        <v>0.584</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="M51">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N51">
         <v>1247</v>
@@ -3286,10 +3227,10 @@
         <v>21933.4</v>
       </c>
       <c r="U51">
-        <v>142.243</v>
+        <v>142.24299999999999</v>
       </c>
       <c r="X51">
-        <v>0.404</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="Y51">
         <v>1.046</v>

--- a/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
@@ -1,291 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5519531C-6A14-4E26-8343-56C82D85B66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="86">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Blue_Shark_NPac</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>6.784</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.146</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.639</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>245.2</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.992</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.496</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.903</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.735</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.032</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.624</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.997</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.05</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.01</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.941</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -385,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -419,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -454,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -630,368 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="43.1796875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>47</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Blue_Shark_NPac</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6.784</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.639</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>245.2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.992</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.496</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.903</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.624</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.997</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.941</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1000,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1971</v>
       </c>
@@ -1089,7 +1067,7 @@
         <v>35800</v>
       </c>
       <c r="G2">
-        <v>1.7729999999999999</v>
+        <v>1.773</v>
       </c>
       <c r="H2">
         <v>440</v>
@@ -1101,7 +1079,7 @@
         <v>35355</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1972</v>
       </c>
@@ -1121,12 +1099,12 @@
         <v>33064</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1973</v>
       </c>
       <c r="B4">
-        <v>34991.800000000003</v>
+        <v>34991.8</v>
       </c>
       <c r="G4">
         <v>1.276</v>
@@ -1138,15 +1116,15 @@
         <v>1</v>
       </c>
       <c r="T4">
-        <v>34550.800000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+        <v>34550.8</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1974</v>
       </c>
       <c r="B5">
-        <v>31292.799999999999</v>
+        <v>31292.8</v>
       </c>
       <c r="G5">
         <v>1.278</v>
@@ -1158,15 +1136,15 @@
         <v>134</v>
       </c>
       <c r="T5">
-        <v>30718.799999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+        <v>30718.8</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>1975</v>
       </c>
       <c r="B6">
-        <v>37346.699999999997</v>
+        <v>37346.7</v>
       </c>
       <c r="G6">
         <v>1.284</v>
@@ -1178,10 +1156,10 @@
         <v>200</v>
       </c>
       <c r="T6">
-        <v>36706.699999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+        <v>36706.7</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>1976</v>
       </c>
@@ -1189,7 +1167,7 @@
         <v>53884.9</v>
       </c>
       <c r="G7">
-        <v>1.2889999999999999</v>
+        <v>1.289</v>
       </c>
       <c r="H7">
         <v>374</v>
@@ -1204,7 +1182,7 @@
         <v>1.341</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1977</v>
       </c>
@@ -1212,7 +1190,7 @@
         <v>69949</v>
       </c>
       <c r="G8">
-        <v>1.2969999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="H8">
         <v>386</v>
@@ -1227,7 +1205,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>1978</v>
       </c>
@@ -1250,12 +1228,12 @@
         <v>1.202</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1979</v>
       </c>
       <c r="B10">
-        <v>68432.399999999994</v>
+        <v>68432.39999999999</v>
       </c>
       <c r="C10">
         <v>114.185</v>
@@ -1264,7 +1242,7 @@
         <v>0.309</v>
       </c>
       <c r="F10">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="G10">
         <v>1.276</v>
@@ -1276,7 +1254,7 @@
         <v>14</v>
       </c>
       <c r="T10">
-        <v>68080.399999999994</v>
+        <v>68080.39999999999</v>
       </c>
       <c r="U10">
         <v>114.185</v>
@@ -1285,13 +1263,13 @@
         <v>0.309</v>
       </c>
       <c r="X10">
-        <v>9.6000000000000002E-2</v>
+        <v>0.096</v>
       </c>
       <c r="Y10">
-        <v>1.2609999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.261</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>1980</v>
       </c>
@@ -1302,13 +1280,13 @@
         <v>106.759</v>
       </c>
       <c r="E11">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="F11">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="G11">
-        <v>1.2370000000000001</v>
+        <v>1.237</v>
       </c>
       <c r="H11">
         <v>336</v>
@@ -1323,16 +1301,16 @@
         <v>106.759</v>
       </c>
       <c r="W11">
-        <v>0.28199999999999997</v>
+        <v>0.282</v>
       </c>
       <c r="X11">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="Y11">
         <v>1.351</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>1981</v>
       </c>
@@ -1340,16 +1318,16 @@
         <v>69958</v>
       </c>
       <c r="C12">
-        <v>132.20699999999999</v>
+        <v>132.207</v>
       </c>
       <c r="E12">
-        <v>0.32700000000000001</v>
+        <v>0.327</v>
       </c>
       <c r="F12">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="G12">
-        <v>1.2070000000000001</v>
+        <v>1.207</v>
       </c>
       <c r="H12">
         <v>256</v>
@@ -1361,19 +1339,19 @@
         <v>69662</v>
       </c>
       <c r="U12">
-        <v>132.20699999999999</v>
+        <v>132.207</v>
       </c>
       <c r="W12">
-        <v>0.32700000000000001</v>
+        <v>0.327</v>
       </c>
       <c r="X12">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="Y12">
-        <v>1.1220000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.122</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1982</v>
       </c>
@@ -1387,7 +1365,7 @@
         <v>0.23</v>
       </c>
       <c r="F13">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="G13">
         <v>1.17</v>
@@ -1408,13 +1386,13 @@
         <v>0.23</v>
       </c>
       <c r="X13">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="Y13">
-        <v>1.1020000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.102</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>1983</v>
       </c>
@@ -1422,16 +1400,16 @@
         <v>52017.4</v>
       </c>
       <c r="C14">
-        <v>153.18199999999999</v>
+        <v>153.182</v>
       </c>
       <c r="E14">
         <v>0.218</v>
       </c>
       <c r="F14">
-        <v>0.51500000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="G14">
-        <v>1.1339999999999999</v>
+        <v>1.134</v>
       </c>
       <c r="H14">
         <v>293</v>
@@ -1443,19 +1421,19 @@
         <v>51719.4</v>
       </c>
       <c r="U14">
-        <v>153.18199999999999</v>
+        <v>153.182</v>
       </c>
       <c r="W14">
         <v>0.218</v>
       </c>
       <c r="X14">
-        <v>0.51500000000000001</v>
+        <v>0.515</v>
       </c>
       <c r="Y14">
-        <v>1.0429999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.043</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1984</v>
       </c>
@@ -1475,10 +1453,10 @@
         <v>49578.3</v>
       </c>
       <c r="Y15">
-        <v>0.90400000000000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>1985</v>
       </c>
@@ -1498,10 +1476,10 @@
         <v>48066.5</v>
       </c>
       <c r="Y16">
-        <v>0.77500000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>1986</v>
       </c>
@@ -1509,7 +1487,7 @@
         <v>43161.1</v>
       </c>
       <c r="G17">
-        <v>1.0509999999999999</v>
+        <v>1.051</v>
       </c>
       <c r="H17">
         <v>407</v>
@@ -1521,18 +1499,18 @@
         <v>42616.1</v>
       </c>
       <c r="Y17">
-        <v>0.90400000000000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1987</v>
       </c>
       <c r="B18">
-        <v>36421.599999999999</v>
+        <v>36421.6</v>
       </c>
       <c r="G18">
-        <v>1.0109999999999999</v>
+        <v>1.011</v>
       </c>
       <c r="H18">
         <v>351</v>
@@ -1544,18 +1522,18 @@
         <v>36014.6</v>
       </c>
       <c r="Y18">
-        <v>0.67500000000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1988</v>
       </c>
       <c r="B19">
-        <v>40902.300000000003</v>
+        <v>40902.3</v>
       </c>
       <c r="G19">
-        <v>0.95599999999999996</v>
+        <v>0.956</v>
       </c>
       <c r="H19">
         <v>509</v>
@@ -1564,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>40383.300000000003</v>
+        <v>40383.3</v>
       </c>
       <c r="Y19">
-        <v>0.70499999999999996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.705</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1989</v>
       </c>
@@ -1578,7 +1556,7 @@
         <v>42514</v>
       </c>
       <c r="G20">
-        <v>0.90200000000000002</v>
+        <v>0.902</v>
       </c>
       <c r="H20">
         <v>280</v>
@@ -1590,10 +1568,10 @@
         <v>42180</v>
       </c>
       <c r="Y20">
-        <v>0.63600000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.636</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1990</v>
       </c>
@@ -1604,13 +1582,13 @@
         <v>118.81</v>
       </c>
       <c r="E21">
-        <v>0.25800000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="F21">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="G21">
-        <v>0.85099999999999998</v>
+        <v>0.851</v>
       </c>
       <c r="H21">
         <v>1130</v>
@@ -1625,16 +1603,16 @@
         <v>118.81</v>
       </c>
       <c r="W21">
-        <v>0.25800000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="X21">
-        <v>9.5000000000000001E-2</v>
+        <v>0.095</v>
       </c>
       <c r="Y21">
-        <v>0.66500000000000004</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.665</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>1991</v>
       </c>
@@ -1642,16 +1620,16 @@
         <v>37515.9</v>
       </c>
       <c r="C22">
-        <v>133.88900000000001</v>
+        <v>133.889</v>
       </c>
       <c r="E22">
         <v>0.37</v>
       </c>
       <c r="F22">
-        <v>0.33300000000000002</v>
+        <v>0.333</v>
       </c>
       <c r="G22">
-        <v>0.79100000000000004</v>
+        <v>0.791</v>
       </c>
       <c r="H22">
         <v>1016</v>
@@ -1663,19 +1641,19 @@
         <v>36269.9</v>
       </c>
       <c r="U22">
-        <v>133.88900000000001</v>
+        <v>133.889</v>
       </c>
       <c r="W22">
         <v>0.37</v>
       </c>
       <c r="X22">
-        <v>0.33300000000000002</v>
+        <v>0.333</v>
       </c>
       <c r="Y22">
-        <v>0.84399999999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>1992</v>
       </c>
@@ -1683,16 +1661,16 @@
         <v>33307.9</v>
       </c>
       <c r="C23">
-        <v>133.79400000000001</v>
+        <v>133.794</v>
       </c>
       <c r="E23">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="F23">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="G23">
-        <v>0.73299999999999998</v>
+        <v>0.733</v>
       </c>
       <c r="H23">
         <v>1636</v>
@@ -1704,19 +1682,19 @@
         <v>31596.9</v>
       </c>
       <c r="U23">
-        <v>133.79400000000001</v>
+        <v>133.794</v>
       </c>
       <c r="W23">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="X23">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="Y23">
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -1754,10 +1732,10 @@
         <v>0.24</v>
       </c>
       <c r="Y24">
-        <v>0.96299999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.963</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1994</v>
       </c>
@@ -1768,13 +1746,13 @@
         <v>124.883</v>
       </c>
       <c r="E25">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="F25">
         <v>0.23</v>
       </c>
       <c r="G25">
-        <v>0.69099999999999995</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H25">
         <v>1758</v>
@@ -1783,22 +1761,22 @@
         <v>12</v>
       </c>
       <c r="T25">
-        <v>41696.699999999997</v>
+        <v>41696.7</v>
       </c>
       <c r="U25">
         <v>124.883</v>
       </c>
       <c r="W25">
-        <v>0.26600000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="X25">
         <v>0.23</v>
       </c>
       <c r="Y25">
-        <v>1.1180000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.118</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1995</v>
       </c>
@@ -1806,16 +1784,16 @@
         <v>47454.6</v>
       </c>
       <c r="C26">
-        <v>140.87899999999999</v>
+        <v>140.879</v>
       </c>
       <c r="E26">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="F26">
         <v>0.376</v>
       </c>
       <c r="G26">
-        <v>0.70399999999999996</v>
+        <v>0.704</v>
       </c>
       <c r="H26">
         <v>2100</v>
@@ -1827,10 +1805,10 @@
         <v>44716.6</v>
       </c>
       <c r="U26">
-        <v>140.87899999999999</v>
+        <v>140.879</v>
       </c>
       <c r="W26">
-        <v>0.17299999999999999</v>
+        <v>0.173</v>
       </c>
       <c r="X26">
         <v>0.376</v>
@@ -1839,7 +1817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27">
         <v>1996</v>
       </c>
@@ -1850,13 +1828,13 @@
         <v>129.017</v>
       </c>
       <c r="E27">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="F27">
-        <v>0.22600000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="G27">
-        <v>0.71899999999999997</v>
+        <v>0.719</v>
       </c>
       <c r="H27">
         <v>3117</v>
@@ -1865,22 +1843,22 @@
         <v>275</v>
       </c>
       <c r="T27">
-        <v>38736.199999999997</v>
+        <v>38736.2</v>
       </c>
       <c r="U27">
         <v>129.017</v>
       </c>
       <c r="W27">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="X27">
-        <v>0.22600000000000001</v>
+        <v>0.226</v>
       </c>
       <c r="Y27">
         <v>1.075</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28">
         <v>1997</v>
       </c>
@@ -1888,16 +1866,16 @@
         <v>47922.7</v>
       </c>
       <c r="C28">
-        <v>135.95400000000001</v>
+        <v>135.954</v>
       </c>
       <c r="E28">
         <v>0.224</v>
       </c>
       <c r="F28">
-        <v>0.29199999999999998</v>
+        <v>0.292</v>
       </c>
       <c r="G28">
-        <v>0.73399999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="H28">
         <v>2948</v>
@@ -1909,19 +1887,19 @@
         <v>44654.7</v>
       </c>
       <c r="U28">
-        <v>135.95400000000001</v>
+        <v>135.954</v>
       </c>
       <c r="W28">
         <v>0.224</v>
       </c>
       <c r="X28">
-        <v>0.29199999999999998</v>
+        <v>0.292</v>
       </c>
       <c r="Y28">
-        <v>1.2130000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.213</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1998</v>
       </c>
@@ -1929,16 +1907,16 @@
         <v>46291.9</v>
       </c>
       <c r="C29">
-        <v>132.15199999999999</v>
+        <v>132.152</v>
       </c>
       <c r="E29">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="F29">
-        <v>0.26900000000000002</v>
+        <v>0.269</v>
       </c>
       <c r="G29">
-        <v>0.74399999999999999</v>
+        <v>0.744</v>
       </c>
       <c r="H29">
         <v>3134</v>
@@ -1950,19 +1928,19 @@
         <v>42820.9</v>
       </c>
       <c r="U29">
-        <v>132.15199999999999</v>
+        <v>132.152</v>
       </c>
       <c r="W29">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="X29">
-        <v>0.26900000000000002</v>
+        <v>0.269</v>
       </c>
       <c r="Y29">
         <v>1.349</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30">
         <v>1999</v>
       </c>
@@ -1970,16 +1948,16 @@
         <v>51535.4</v>
       </c>
       <c r="C30">
-        <v>136.63200000000001</v>
+        <v>136.632</v>
       </c>
       <c r="E30">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F30">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="G30">
-        <v>0.76700000000000002</v>
+        <v>0.767</v>
       </c>
       <c r="H30">
         <v>2261</v>
@@ -1991,19 +1969,19 @@
         <v>48651.4</v>
       </c>
       <c r="U30">
-        <v>136.63200000000001</v>
+        <v>136.632</v>
       </c>
       <c r="W30">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="X30">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="Y30">
-        <v>1.2989999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.299</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>2000</v>
       </c>
@@ -2011,16 +1989,16 @@
         <v>55109.2</v>
       </c>
       <c r="C31">
-        <v>144.05099999999999</v>
+        <v>144.051</v>
       </c>
       <c r="E31">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="F31">
-        <v>0.41799999999999998</v>
+        <v>0.418</v>
       </c>
       <c r="G31">
-        <v>0.79800000000000004</v>
+        <v>0.798</v>
       </c>
       <c r="H31">
         <v>2719</v>
@@ -2032,19 +2010,19 @@
         <v>51706.2</v>
       </c>
       <c r="U31">
-        <v>144.05099999999999</v>
+        <v>144.051</v>
       </c>
       <c r="W31">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="X31">
-        <v>0.41799999999999998</v>
+        <v>0.418</v>
       </c>
       <c r="Y31">
-        <v>1.1919999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.192</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>2001</v>
       </c>
@@ -2061,7 +2039,7 @@
         <v>0.375</v>
       </c>
       <c r="G32">
-        <v>0.84199999999999997</v>
+        <v>0.842</v>
       </c>
       <c r="H32">
         <v>2587</v>
@@ -2085,7 +2063,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33">
         <v>2002</v>
       </c>
@@ -2093,13 +2071,13 @@
         <v>44311</v>
       </c>
       <c r="C33">
-        <v>142.81899999999999</v>
+        <v>142.819</v>
       </c>
       <c r="E33">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="F33">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="G33">
         <v>0.88</v>
@@ -2114,36 +2092,36 @@
         <v>40430</v>
       </c>
       <c r="U33">
-        <v>142.81899999999999</v>
+        <v>142.819</v>
       </c>
       <c r="W33">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="X33">
-        <v>0.40899999999999997</v>
+        <v>0.409</v>
       </c>
       <c r="Y33">
         <v>1.052</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34">
         <v>2003</v>
       </c>
       <c r="B34">
-        <v>40435.300000000003</v>
+        <v>40435.3</v>
       </c>
       <c r="C34">
         <v>141.6</v>
       </c>
       <c r="E34">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="F34">
-        <v>0.35899999999999999</v>
+        <v>0.359</v>
       </c>
       <c r="G34">
-        <v>0.90600000000000003</v>
+        <v>0.906</v>
       </c>
       <c r="H34">
         <v>2307</v>
@@ -2152,22 +2130,22 @@
         <v>777</v>
       </c>
       <c r="T34">
-        <v>37351.300000000003</v>
+        <v>37351.3</v>
       </c>
       <c r="U34">
         <v>141.6</v>
       </c>
       <c r="W34">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="X34">
-        <v>0.35899999999999999</v>
+        <v>0.359</v>
       </c>
       <c r="Y34">
         <v>1.087</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35">
         <v>2004</v>
       </c>
@@ -2181,10 +2159,10 @@
         <v>0.217</v>
       </c>
       <c r="F35">
-        <v>0.40300000000000002</v>
+        <v>0.403</v>
       </c>
       <c r="G35">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H35">
         <v>3781</v>
@@ -2193,19 +2171,19 @@
         <v>1189</v>
       </c>
       <c r="O35">
-        <v>179.06200000000001</v>
+        <v>179.062</v>
       </c>
       <c r="Q35">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="R35">
-        <v>0.81200000000000006</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="S35">
         <v>0.24</v>
       </c>
       <c r="T35">
-        <v>37744.300000000003</v>
+        <v>37744.3</v>
       </c>
       <c r="U35">
         <v>140.94</v>
@@ -2214,13 +2192,13 @@
         <v>0.219</v>
       </c>
       <c r="X35">
-        <v>0.33500000000000002</v>
+        <v>0.335</v>
       </c>
       <c r="Y35">
-        <v>1.0640000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.064</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>2005</v>
       </c>
@@ -2228,7 +2206,7 @@
         <v>43812.3</v>
       </c>
       <c r="C36">
-        <v>156.71799999999999</v>
+        <v>156.718</v>
       </c>
       <c r="E36">
         <v>0.224</v>
@@ -2237,7 +2215,7 @@
         <v>0.5</v>
       </c>
       <c r="G36">
-        <v>0.95799999999999996</v>
+        <v>0.958</v>
       </c>
       <c r="H36">
         <v>2721</v>
@@ -2246,25 +2224,25 @@
         <v>915</v>
       </c>
       <c r="O36">
-        <v>208.02600000000001</v>
+        <v>208.026</v>
       </c>
       <c r="Q36">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="R36">
-        <v>0.86799999999999999</v>
+        <v>0.868</v>
       </c>
       <c r="S36">
         <v>1.4</v>
       </c>
       <c r="T36">
-        <v>40176.300000000003</v>
+        <v>40176.3</v>
       </c>
       <c r="U36">
         <v>148.167</v>
       </c>
       <c r="W36">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="X36">
         <v>0.439</v>
@@ -2273,12 +2251,12 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37">
         <v>2006</v>
       </c>
       <c r="B37">
-        <v>40258.300000000003</v>
+        <v>40258.3</v>
       </c>
       <c r="C37">
         <v>154.738</v>
@@ -2287,22 +2265,22 @@
         <v>0.222</v>
       </c>
       <c r="F37">
-        <v>0.47499999999999998</v>
+        <v>0.475</v>
       </c>
       <c r="G37">
-        <v>0.97799999999999998</v>
+        <v>0.978</v>
       </c>
       <c r="H37">
         <v>2765</v>
       </c>
       <c r="I37">
-        <v>130.76400000000001</v>
+        <v>130.764</v>
       </c>
       <c r="K37">
         <v>0.248</v>
       </c>
       <c r="L37">
-        <v>0.19900000000000001</v>
+        <v>0.199</v>
       </c>
       <c r="M37">
         <v>1.321</v>
@@ -2311,34 +2289,34 @@
         <v>884</v>
       </c>
       <c r="O37">
-        <v>194.36699999999999</v>
+        <v>194.367</v>
       </c>
       <c r="Q37">
         <v>0.219</v>
       </c>
       <c r="R37">
-        <v>0.84799999999999998</v>
+        <v>0.848</v>
       </c>
       <c r="S37">
         <v>0.8</v>
       </c>
       <c r="T37">
-        <v>36609.300000000003</v>
+        <v>36609.3</v>
       </c>
       <c r="U37">
-        <v>152.12899999999999</v>
+        <v>152.129</v>
       </c>
       <c r="W37">
         <v>0.219</v>
       </c>
       <c r="X37">
-        <v>0.45900000000000002</v>
+        <v>0.459</v>
       </c>
       <c r="Y37">
         <v>0.877</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -2346,25 +2324,25 @@
         <v>38605.4</v>
       </c>
       <c r="C38">
-        <v>152.37100000000001</v>
+        <v>152.371</v>
       </c>
       <c r="E38">
-        <v>0.23599999999999999</v>
+        <v>0.236</v>
       </c>
       <c r="F38">
         <v>0.435</v>
       </c>
       <c r="G38">
-        <v>0.99099999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="H38">
         <v>3324</v>
       </c>
       <c r="I38">
-        <v>135.09100000000001</v>
+        <v>135.091</v>
       </c>
       <c r="K38">
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="L38">
         <v>0.249</v>
@@ -2376,13 +2354,13 @@
         <v>818</v>
       </c>
       <c r="O38">
-        <v>188.17099999999999</v>
+        <v>188.171</v>
       </c>
       <c r="Q38">
         <v>0.248</v>
       </c>
       <c r="R38">
-        <v>0.73199999999999998</v>
+        <v>0.732</v>
       </c>
       <c r="S38">
         <v>0.51</v>
@@ -2394,16 +2372,16 @@
         <v>149.285</v>
       </c>
       <c r="W38">
-        <v>0.23300000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="X38">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="Y38">
-        <v>0.80800000000000005</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.8080000000000001</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2008</v>
       </c>
@@ -2411,16 +2389,16 @@
         <v>36373</v>
       </c>
       <c r="C39">
-        <v>148.22999999999999</v>
+        <v>148.23</v>
       </c>
       <c r="E39">
         <v>0.23</v>
       </c>
       <c r="F39">
-        <v>0.41399999999999998</v>
+        <v>0.414</v>
       </c>
       <c r="G39">
-        <v>0.99399999999999999</v>
+        <v>0.994</v>
       </c>
       <c r="H39">
         <v>4355</v>
@@ -2429,46 +2407,46 @@
         <v>140.279</v>
       </c>
       <c r="K39">
-        <v>0.20100000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="L39">
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="M39">
-        <v>1.2609999999999999</v>
+        <v>1.261</v>
       </c>
       <c r="N39">
         <v>680</v>
       </c>
       <c r="O39">
-        <v>204.07400000000001</v>
+        <v>204.074</v>
       </c>
       <c r="Q39">
         <v>0.183</v>
       </c>
       <c r="R39">
-        <v>0.90700000000000003</v>
+        <v>0.907</v>
       </c>
       <c r="S39">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T39">
         <v>31338</v>
       </c>
       <c r="U39">
-        <v>141.38800000000001</v>
+        <v>141.388</v>
       </c>
       <c r="W39">
-        <v>0.24099999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="X39">
-        <v>0.36799999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="Y39">
         <v>0.623</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40">
         <v>2009</v>
       </c>
@@ -2485,69 +2463,69 @@
         <v>0.434</v>
       </c>
       <c r="G40">
-        <v>0.98499999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="H40">
         <v>4423</v>
       </c>
       <c r="I40">
-        <v>143.26499999999999</v>
+        <v>143.265</v>
       </c>
       <c r="K40">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="L40">
-        <v>0.24099999999999999</v>
+        <v>0.241</v>
       </c>
       <c r="M40">
-        <v>0.99099999999999999</v>
+        <v>0.991</v>
       </c>
       <c r="N40">
         <v>478</v>
       </c>
       <c r="O40">
-        <v>191.75700000000001</v>
+        <v>191.757</v>
       </c>
       <c r="Q40">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="R40">
-        <v>0.78400000000000003</v>
+        <v>0.784</v>
       </c>
       <c r="S40">
         <v>0.41</v>
       </c>
       <c r="T40">
-        <v>34101.599999999999</v>
+        <v>34101.6</v>
       </c>
       <c r="U40">
-        <v>146.43199999999999</v>
+        <v>146.432</v>
       </c>
       <c r="W40">
-        <v>0.26900000000000002</v>
+        <v>0.269</v>
       </c>
       <c r="X40">
-        <v>0.40799999999999997</v>
+        <v>0.408</v>
       </c>
       <c r="Y40">
-        <v>0.71399999999999997</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.714</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>2010</v>
       </c>
       <c r="B41">
-        <v>36524.300000000003</v>
+        <v>36524.3</v>
       </c>
       <c r="C41">
-        <v>147.52600000000001</v>
+        <v>147.526</v>
       </c>
       <c r="E41">
-        <v>0.24299999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="F41">
-        <v>0.40400000000000003</v>
+        <v>0.404</v>
       </c>
       <c r="G41">
         <v>0.96</v>
@@ -2556,25 +2534,25 @@
         <v>4469</v>
       </c>
       <c r="I41">
-        <v>146.34800000000001</v>
+        <v>146.348</v>
       </c>
       <c r="K41">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="L41">
         <v>0.316</v>
       </c>
       <c r="M41">
-        <v>0.83099999999999996</v>
+        <v>0.831</v>
       </c>
       <c r="N41">
         <v>334</v>
       </c>
       <c r="O41">
-        <v>181.55600000000001</v>
+        <v>181.556</v>
       </c>
       <c r="Q41">
-        <v>0.14599999999999999</v>
+        <v>0.146</v>
       </c>
       <c r="R41">
         <v>0.8</v>
@@ -2586,19 +2564,19 @@
         <v>31721.3</v>
       </c>
       <c r="U41">
-        <v>140.95599999999999</v>
+        <v>140.956</v>
       </c>
       <c r="W41">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="X41">
-        <v>0.34200000000000003</v>
+        <v>0.342</v>
       </c>
       <c r="Y41">
         <v>0.87</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42">
         <v>2011</v>
       </c>
@@ -2606,64 +2584,64 @@
         <v>31164.6</v>
       </c>
       <c r="C42">
-        <v>146.08199999999999</v>
+        <v>146.082</v>
       </c>
       <c r="E42">
-        <v>0.23400000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="F42">
-        <v>0.40600000000000003</v>
+        <v>0.406</v>
       </c>
       <c r="G42">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H42">
         <v>3719</v>
       </c>
       <c r="I42">
-        <v>139.52799999999999</v>
+        <v>139.528</v>
       </c>
       <c r="K42">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="L42">
-        <v>0.29399999999999998</v>
+        <v>0.294</v>
       </c>
       <c r="M42">
-        <v>0.76100000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="N42">
         <v>594</v>
       </c>
       <c r="O42">
-        <v>189.86799999999999</v>
+        <v>189.868</v>
       </c>
       <c r="Q42">
         <v>0.127</v>
       </c>
       <c r="R42">
-        <v>0.89500000000000002</v>
+        <v>0.895</v>
       </c>
       <c r="S42">
         <v>0.74</v>
       </c>
       <c r="T42">
-        <v>26851.599999999999</v>
+        <v>26851.6</v>
       </c>
       <c r="U42">
-        <v>140.76300000000001</v>
+        <v>140.763</v>
       </c>
       <c r="W42">
         <v>0.246</v>
       </c>
       <c r="X42">
-        <v>0.35199999999999998</v>
+        <v>0.352</v>
       </c>
       <c r="Y42">
-        <v>0.79800000000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.798</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>2012</v>
       </c>
@@ -2671,22 +2649,22 @@
         <v>33863</v>
       </c>
       <c r="C43">
-        <v>146.06200000000001</v>
+        <v>146.062</v>
       </c>
       <c r="E43">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="F43">
-        <v>0.39700000000000002</v>
+        <v>0.397</v>
       </c>
       <c r="G43">
-        <v>0.92300000000000004</v>
+        <v>0.923</v>
       </c>
       <c r="H43">
         <v>4108</v>
       </c>
       <c r="I43">
-        <v>134.83699999999999</v>
+        <v>134.837</v>
       </c>
       <c r="K43">
         <v>0.189</v>
@@ -2695,7 +2673,7 @@
         <v>0.17</v>
       </c>
       <c r="M43">
-        <v>1.2310000000000001</v>
+        <v>1.231</v>
       </c>
       <c r="N43">
         <v>594</v>
@@ -2704,7 +2682,7 @@
         <v>173.774</v>
       </c>
       <c r="Q43">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="R43">
         <v>0.66</v>
@@ -2716,19 +2694,19 @@
         <v>29161</v>
       </c>
       <c r="U43">
-        <v>144.22999999999999</v>
+        <v>144.23</v>
       </c>
       <c r="W43">
         <v>0.216</v>
       </c>
       <c r="X43">
-        <v>0.39300000000000002</v>
+        <v>0.393</v>
       </c>
       <c r="Y43">
         <v>0.752</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44">
         <v>2013</v>
       </c>
@@ -2736,46 +2714,46 @@
         <v>26212.7</v>
       </c>
       <c r="C44">
-        <v>153.71299999999999</v>
+        <v>153.713</v>
       </c>
       <c r="E44">
         <v>0.224</v>
       </c>
       <c r="F44">
-        <v>0.47399999999999998</v>
+        <v>0.474</v>
       </c>
       <c r="G44">
-        <v>0.91700000000000004</v>
+        <v>0.917</v>
       </c>
       <c r="H44">
         <v>4494</v>
       </c>
       <c r="I44">
-        <v>137.90700000000001</v>
+        <v>137.907</v>
       </c>
       <c r="K44">
         <v>0.182</v>
       </c>
       <c r="L44">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="M44">
-        <v>1.2809999999999999</v>
+        <v>1.281</v>
       </c>
       <c r="N44">
         <v>551</v>
       </c>
       <c r="O44">
-        <v>168.68899999999999</v>
+        <v>168.689</v>
       </c>
       <c r="Q44">
         <v>0.15</v>
       </c>
       <c r="R44">
-        <v>0.73799999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="S44">
-        <v>1.0900000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="T44">
         <v>21167.7</v>
@@ -2784,16 +2762,16 @@
         <v>153.816</v>
       </c>
       <c r="W44">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="X44">
-        <v>0.47699999999999998</v>
+        <v>0.477</v>
       </c>
       <c r="Y44">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.838</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>2014</v>
       </c>
@@ -2807,22 +2785,22 @@
         <v>0.21</v>
       </c>
       <c r="F45">
-        <v>0.40699999999999997</v>
+        <v>0.407</v>
       </c>
       <c r="G45">
-        <v>0.91300000000000003</v>
+        <v>0.913</v>
       </c>
       <c r="H45">
         <v>5502</v>
       </c>
       <c r="I45">
-        <v>136.14599999999999</v>
+        <v>136.146</v>
       </c>
       <c r="K45">
         <v>0.185</v>
       </c>
       <c r="L45">
-        <v>0.17599999999999999</v>
+        <v>0.176</v>
       </c>
       <c r="M45">
         <v>1.101</v>
@@ -2834,10 +2812,10 @@
         <v>176.714</v>
       </c>
       <c r="Q45">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="R45">
-        <v>0.77100000000000002</v>
+        <v>0.771</v>
       </c>
       <c r="S45">
         <v>0.7</v>
@@ -2846,7 +2824,7 @@
         <v>25388.5</v>
       </c>
       <c r="U45">
-        <v>146.68100000000001</v>
+        <v>146.681</v>
       </c>
       <c r="W45">
         <v>0.221</v>
@@ -2855,10 +2833,10 @@
         <v>0.39</v>
       </c>
       <c r="Y45">
-        <v>1.0029999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.003</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>2015</v>
       </c>
@@ -2866,28 +2844,28 @@
         <v>26372.3</v>
       </c>
       <c r="C46">
-        <v>154.33699999999999</v>
+        <v>154.337</v>
       </c>
       <c r="F46">
-        <v>0.47699999999999998</v>
+        <v>0.477</v>
       </c>
       <c r="G46">
-        <v>0.90700000000000003</v>
+        <v>0.907</v>
       </c>
       <c r="H46">
         <v>3985</v>
       </c>
       <c r="I46">
-        <v>138.61500000000001</v>
+        <v>138.615</v>
       </c>
       <c r="K46">
-        <v>0.16200000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="L46">
         <v>0.159</v>
       </c>
       <c r="M46">
-        <v>0.78100000000000003</v>
+        <v>0.781</v>
       </c>
       <c r="N46">
         <v>1186</v>
@@ -2899,7 +2877,7 @@
         <v>0.192</v>
       </c>
       <c r="R46">
-        <v>0.79800000000000004</v>
+        <v>0.798</v>
       </c>
       <c r="S46">
         <v>1.59</v>
@@ -2908,16 +2886,16 @@
         <v>21201.3</v>
       </c>
       <c r="U46">
-        <v>150.75700000000001</v>
+        <v>150.757</v>
       </c>
       <c r="X46">
-        <v>0.47599999999999998</v>
+        <v>0.476</v>
       </c>
       <c r="Y46">
         <v>1.01</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>2016</v>
       </c>
@@ -2928,13 +2906,13 @@
         <v>157.989</v>
       </c>
       <c r="E47">
-        <v>0.19500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="F47">
-        <v>0.50900000000000001</v>
+        <v>0.509</v>
       </c>
       <c r="G47">
-        <v>0.91600000000000004</v>
+        <v>0.916</v>
       </c>
       <c r="H47">
         <v>4973</v>
@@ -2943,37 +2921,37 @@
         <v>145.745</v>
       </c>
       <c r="K47">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="L47">
-        <v>0.33800000000000002</v>
+        <v>0.338</v>
       </c>
       <c r="M47">
-        <v>1.0509999999999999</v>
+        <v>1.051</v>
       </c>
       <c r="N47">
         <v>430</v>
       </c>
       <c r="O47">
-        <v>199.94499999999999</v>
+        <v>199.945</v>
       </c>
       <c r="Q47">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="R47">
-        <v>0.79100000000000004</v>
+        <v>0.791</v>
       </c>
       <c r="S47">
         <v>1.21</v>
       </c>
       <c r="T47">
-        <v>23775.599999999999</v>
+        <v>23775.6</v>
       </c>
       <c r="U47">
         <v>155.017</v>
       </c>
       <c r="W47">
-        <v>0.19700000000000001</v>
+        <v>0.197</v>
       </c>
       <c r="X47">
         <v>0.498</v>
@@ -2982,7 +2960,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48">
         <v>2017</v>
       </c>
@@ -2993,13 +2971,13 @@
         <v>148.298</v>
       </c>
       <c r="E48">
-        <v>0.20499999999999999</v>
+        <v>0.205</v>
       </c>
       <c r="F48">
-        <v>0.41699999999999998</v>
+        <v>0.417</v>
       </c>
       <c r="G48">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H48">
         <v>3384</v>
@@ -3008,10 +2986,10 @@
         <v>147.797</v>
       </c>
       <c r="K48">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="L48">
-        <v>0.33200000000000002</v>
+        <v>0.332</v>
       </c>
       <c r="M48">
         <v>0.74</v>
@@ -3020,19 +2998,19 @@
         <v>367</v>
       </c>
       <c r="O48">
-        <v>155.89500000000001</v>
+        <v>155.895</v>
       </c>
       <c r="Q48">
         <v>0.121</v>
       </c>
       <c r="R48">
-        <v>0.45300000000000001</v>
+        <v>0.453</v>
       </c>
       <c r="S48">
         <v>1.55</v>
       </c>
       <c r="T48">
-        <v>24646.400000000001</v>
+        <v>24646.4</v>
       </c>
       <c r="U48">
         <v>147.51</v>
@@ -3041,13 +3019,13 @@
         <v>0.218</v>
       </c>
       <c r="X48">
-        <v>0.42199999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="Y48">
-        <v>1.1060000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.106</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2018</v>
       </c>
@@ -3061,25 +3039,25 @@
         <v>0.192</v>
       </c>
       <c r="F49">
-        <v>0.49299999999999999</v>
+        <v>0.493</v>
       </c>
       <c r="G49">
-        <v>0.97399999999999998</v>
+        <v>0.974</v>
       </c>
       <c r="H49">
         <v>2852</v>
       </c>
       <c r="I49">
-        <v>153.59100000000001</v>
+        <v>153.591</v>
       </c>
       <c r="K49">
-        <v>0.14199999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="L49">
-        <v>0.36599999999999999</v>
+        <v>0.366</v>
       </c>
       <c r="M49">
-        <v>0.91100000000000003</v>
+        <v>0.911</v>
       </c>
       <c r="N49">
         <v>402</v>
@@ -3088,10 +3066,10 @@
         <v>167.125</v>
       </c>
       <c r="Q49">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="R49">
-        <v>0.67500000000000004</v>
+        <v>0.675</v>
       </c>
       <c r="S49">
         <v>1.22</v>
@@ -3103,16 +3081,16 @@
         <v>153.107</v>
       </c>
       <c r="W49">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="X49">
-        <v>0.48699999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="Y49">
-        <v>1.0449999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.045</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2019</v>
       </c>
@@ -3126,7 +3104,7 @@
         <v>0.185</v>
       </c>
       <c r="F50">
-        <v>0.49399999999999999</v>
+        <v>0.494</v>
       </c>
       <c r="G50">
         <v>1.006</v>
@@ -3138,10 +3116,10 @@
         <v>154.19</v>
       </c>
       <c r="K50">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="L50">
-        <v>0.53300000000000003</v>
+        <v>0.533</v>
       </c>
       <c r="M50">
         <v>1.101</v>
@@ -3150,13 +3128,13 @@
         <v>1298</v>
       </c>
       <c r="O50">
-        <v>192.30799999999999</v>
+        <v>192.308</v>
       </c>
       <c r="Q50">
-        <v>0.13200000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="R50">
-        <v>0.92300000000000004</v>
+        <v>0.923</v>
       </c>
       <c r="S50">
         <v>1.46</v>
@@ -3165,19 +3143,19 @@
         <v>26927.5</v>
       </c>
       <c r="U50">
-        <v>148.43600000000001</v>
+        <v>148.436</v>
       </c>
       <c r="W50">
         <v>0.188</v>
       </c>
       <c r="X50">
-        <v>0.44700000000000001</v>
+        <v>0.447</v>
       </c>
       <c r="Y50">
         <v>1.044</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51">
         <v>2020</v>
       </c>
@@ -3185,28 +3163,28 @@
         <v>26713.4</v>
       </c>
       <c r="C51">
-        <v>146.37299999999999</v>
+        <v>146.373</v>
       </c>
       <c r="F51">
-        <v>0.44900000000000001</v>
+        <v>0.449</v>
       </c>
       <c r="G51">
-        <v>1.0229999999999999</v>
+        <v>1.023</v>
       </c>
       <c r="H51">
         <v>3533</v>
       </c>
       <c r="I51">
-        <v>156.40700000000001</v>
+        <v>156.407</v>
       </c>
       <c r="K51">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="L51">
-        <v>0.58399999999999996</v>
+        <v>0.584</v>
       </c>
       <c r="M51">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="N51">
         <v>1247</v>
@@ -3227,10 +3205,10 @@
         <v>21933.4</v>
       </c>
       <c r="U51">
-        <v>142.24299999999999</v>
+        <v>142.243</v>
       </c>
       <c r="X51">
-        <v>0.40400000000000003</v>
+        <v>0.404</v>
       </c>
       <c r="Y51">
         <v>1.046</v>

--- a/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_NPac.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>245.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>245.2</t>
+          <t>0.639</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2170,18 +2171,6 @@
       <c r="N35">
         <v>1189</v>
       </c>
-      <c r="O35">
-        <v>179.062</v>
-      </c>
-      <c r="Q35">
-        <v>0.201</v>
-      </c>
-      <c r="R35">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="S35">
-        <v>0.24</v>
-      </c>
       <c r="T35">
         <v>37744.3</v>
       </c>
@@ -2223,18 +2212,6 @@
       <c r="N36">
         <v>915</v>
       </c>
-      <c r="O36">
-        <v>208.026</v>
-      </c>
-      <c r="Q36">
-        <v>0.205</v>
-      </c>
-      <c r="R36">
-        <v>0.868</v>
-      </c>
-      <c r="S36">
-        <v>1.4</v>
-      </c>
       <c r="T36">
         <v>40176.3</v>
       </c>
@@ -2273,32 +2250,8 @@
       <c r="H37">
         <v>2765</v>
       </c>
-      <c r="I37">
-        <v>130.764</v>
-      </c>
-      <c r="K37">
-        <v>0.248</v>
-      </c>
-      <c r="L37">
-        <v>0.199</v>
-      </c>
-      <c r="M37">
-        <v>1.321</v>
-      </c>
       <c r="N37">
         <v>884</v>
-      </c>
-      <c r="O37">
-        <v>194.367</v>
-      </c>
-      <c r="Q37">
-        <v>0.219</v>
-      </c>
-      <c r="R37">
-        <v>0.848</v>
-      </c>
-      <c r="S37">
-        <v>0.8</v>
       </c>
       <c r="T37">
         <v>36609.3</v>
@@ -2338,32 +2291,8 @@
       <c r="H38">
         <v>3324</v>
       </c>
-      <c r="I38">
-        <v>135.091</v>
-      </c>
-      <c r="K38">
-        <v>0.243</v>
-      </c>
-      <c r="L38">
-        <v>0.249</v>
-      </c>
-      <c r="M38">
-        <v>1.071</v>
-      </c>
       <c r="N38">
         <v>818</v>
-      </c>
-      <c r="O38">
-        <v>188.171</v>
-      </c>
-      <c r="Q38">
-        <v>0.248</v>
-      </c>
-      <c r="R38">
-        <v>0.732</v>
-      </c>
-      <c r="S38">
-        <v>0.51</v>
       </c>
       <c r="T38">
         <v>34463.4</v>
@@ -2403,32 +2332,8 @@
       <c r="H39">
         <v>4355</v>
       </c>
-      <c r="I39">
-        <v>140.279</v>
-      </c>
-      <c r="K39">
-        <v>0.201</v>
-      </c>
-      <c r="L39">
-        <v>0.243</v>
-      </c>
-      <c r="M39">
-        <v>1.261</v>
-      </c>
       <c r="N39">
         <v>680</v>
-      </c>
-      <c r="O39">
-        <v>204.074</v>
-      </c>
-      <c r="Q39">
-        <v>0.183</v>
-      </c>
-      <c r="R39">
-        <v>0.907</v>
-      </c>
-      <c r="S39">
-        <v>0.6899999999999999</v>
       </c>
       <c r="T39">
         <v>31338</v>
@@ -2468,32 +2373,8 @@
       <c r="H40">
         <v>4423</v>
       </c>
-      <c r="I40">
-        <v>143.265</v>
-      </c>
-      <c r="K40">
-        <v>0.179</v>
-      </c>
-      <c r="L40">
-        <v>0.241</v>
-      </c>
-      <c r="M40">
-        <v>0.991</v>
-      </c>
       <c r="N40">
         <v>478</v>
-      </c>
-      <c r="O40">
-        <v>191.757</v>
-      </c>
-      <c r="Q40">
-        <v>0.227</v>
-      </c>
-      <c r="R40">
-        <v>0.784</v>
-      </c>
-      <c r="S40">
-        <v>0.41</v>
       </c>
       <c r="T40">
         <v>34101.6</v>
@@ -2533,32 +2414,8 @@
       <c r="H41">
         <v>4469</v>
       </c>
-      <c r="I41">
-        <v>146.348</v>
-      </c>
-      <c r="K41">
-        <v>0.178</v>
-      </c>
-      <c r="L41">
-        <v>0.316</v>
-      </c>
-      <c r="M41">
-        <v>0.831</v>
-      </c>
       <c r="N41">
         <v>334</v>
-      </c>
-      <c r="O41">
-        <v>181.556</v>
-      </c>
-      <c r="Q41">
-        <v>0.146</v>
-      </c>
-      <c r="R41">
-        <v>0.8</v>
-      </c>
-      <c r="S41">
-        <v>0.97</v>
       </c>
       <c r="T41">
         <v>31721.3</v>
@@ -2598,32 +2455,8 @@
       <c r="H42">
         <v>3719</v>
       </c>
-      <c r="I42">
-        <v>139.528</v>
-      </c>
-      <c r="K42">
-        <v>0.257</v>
-      </c>
-      <c r="L42">
-        <v>0.294</v>
-      </c>
-      <c r="M42">
-        <v>0.761</v>
-      </c>
       <c r="N42">
         <v>594</v>
-      </c>
-      <c r="O42">
-        <v>189.868</v>
-      </c>
-      <c r="Q42">
-        <v>0.127</v>
-      </c>
-      <c r="R42">
-        <v>0.895</v>
-      </c>
-      <c r="S42">
-        <v>0.74</v>
       </c>
       <c r="T42">
         <v>26851.6</v>
@@ -2663,32 +2496,8 @@
       <c r="H43">
         <v>4108</v>
       </c>
-      <c r="I43">
-        <v>134.837</v>
-      </c>
-      <c r="K43">
-        <v>0.189</v>
-      </c>
-      <c r="L43">
-        <v>0.17</v>
-      </c>
-      <c r="M43">
-        <v>1.231</v>
-      </c>
       <c r="N43">
         <v>594</v>
-      </c>
-      <c r="O43">
-        <v>173.774</v>
-      </c>
-      <c r="Q43">
-        <v>0.197</v>
-      </c>
-      <c r="R43">
-        <v>0.66</v>
-      </c>
-      <c r="S43">
-        <v>1.03</v>
       </c>
       <c r="T43">
         <v>29161</v>
@@ -2728,32 +2537,8 @@
       <c r="H44">
         <v>4494</v>
       </c>
-      <c r="I44">
-        <v>137.907</v>
-      </c>
-      <c r="K44">
-        <v>0.182</v>
-      </c>
-      <c r="L44">
-        <v>0.178</v>
-      </c>
-      <c r="M44">
-        <v>1.281</v>
-      </c>
       <c r="N44">
         <v>551</v>
-      </c>
-      <c r="O44">
-        <v>168.689</v>
-      </c>
-      <c r="Q44">
-        <v>0.15</v>
-      </c>
-      <c r="R44">
-        <v>0.738</v>
-      </c>
-      <c r="S44">
-        <v>1.09</v>
       </c>
       <c r="T44">
         <v>21167.7</v>
@@ -2793,32 +2578,8 @@
       <c r="H45">
         <v>5502</v>
       </c>
-      <c r="I45">
-        <v>136.146</v>
-      </c>
-      <c r="K45">
-        <v>0.185</v>
-      </c>
-      <c r="L45">
-        <v>0.176</v>
-      </c>
-      <c r="M45">
-        <v>1.101</v>
-      </c>
       <c r="N45">
         <v>700</v>
-      </c>
-      <c r="O45">
-        <v>176.714</v>
-      </c>
-      <c r="Q45">
-        <v>0.143</v>
-      </c>
-      <c r="R45">
-        <v>0.771</v>
-      </c>
-      <c r="S45">
-        <v>0.7</v>
       </c>
       <c r="T45">
         <v>25388.5</v>
@@ -2855,32 +2616,8 @@
       <c r="H46">
         <v>3985</v>
       </c>
-      <c r="I46">
-        <v>138.615</v>
-      </c>
-      <c r="K46">
-        <v>0.162</v>
-      </c>
-      <c r="L46">
-        <v>0.159</v>
-      </c>
-      <c r="M46">
-        <v>0.781</v>
-      </c>
       <c r="N46">
         <v>1186</v>
-      </c>
-      <c r="O46">
-        <v>198.697</v>
-      </c>
-      <c r="Q46">
-        <v>0.192</v>
-      </c>
-      <c r="R46">
-        <v>0.798</v>
-      </c>
-      <c r="S46">
-        <v>1.59</v>
       </c>
       <c r="T46">
         <v>21201.3</v>
@@ -2917,32 +2654,8 @@
       <c r="H47">
         <v>4973</v>
       </c>
-      <c r="I47">
-        <v>145.745</v>
-      </c>
-      <c r="K47">
-        <v>0.175</v>
-      </c>
-      <c r="L47">
-        <v>0.338</v>
-      </c>
-      <c r="M47">
-        <v>1.051</v>
-      </c>
       <c r="N47">
         <v>430</v>
-      </c>
-      <c r="O47">
-        <v>199.945</v>
-      </c>
-      <c r="Q47">
-        <v>0.196</v>
-      </c>
-      <c r="R47">
-        <v>0.791</v>
-      </c>
-      <c r="S47">
-        <v>1.21</v>
       </c>
       <c r="T47">
         <v>23775.6</v>
@@ -2982,32 +2695,8 @@
       <c r="H48">
         <v>3384</v>
       </c>
-      <c r="I48">
-        <v>147.797</v>
-      </c>
-      <c r="K48">
-        <v>0.177</v>
-      </c>
-      <c r="L48">
-        <v>0.332</v>
-      </c>
-      <c r="M48">
-        <v>0.74</v>
-      </c>
       <c r="N48">
         <v>367</v>
-      </c>
-      <c r="O48">
-        <v>155.895</v>
-      </c>
-      <c r="Q48">
-        <v>0.121</v>
-      </c>
-      <c r="R48">
-        <v>0.453</v>
-      </c>
-      <c r="S48">
-        <v>1.55</v>
       </c>
       <c r="T48">
         <v>24646.4</v>
@@ -3047,32 +2736,8 @@
       <c r="H49">
         <v>2852</v>
       </c>
-      <c r="I49">
-        <v>153.591</v>
-      </c>
-      <c r="K49">
-        <v>0.142</v>
-      </c>
-      <c r="L49">
-        <v>0.366</v>
-      </c>
-      <c r="M49">
-        <v>0.911</v>
-      </c>
       <c r="N49">
         <v>402</v>
-      </c>
-      <c r="O49">
-        <v>167.125</v>
-      </c>
-      <c r="Q49">
-        <v>0.137</v>
-      </c>
-      <c r="R49">
-        <v>0.675</v>
-      </c>
-      <c r="S49">
-        <v>1.22</v>
       </c>
       <c r="T49">
         <v>23477.1</v>
@@ -3112,32 +2777,8 @@
       <c r="H50">
         <v>3772</v>
       </c>
-      <c r="I50">
-        <v>154.19</v>
-      </c>
-      <c r="K50">
-        <v>0.203</v>
-      </c>
-      <c r="L50">
-        <v>0.533</v>
-      </c>
-      <c r="M50">
-        <v>1.101</v>
-      </c>
       <c r="N50">
         <v>1298</v>
-      </c>
-      <c r="O50">
-        <v>192.308</v>
-      </c>
-      <c r="Q50">
-        <v>0.132</v>
-      </c>
-      <c r="R50">
-        <v>0.923</v>
-      </c>
-      <c r="S50">
-        <v>1.46</v>
       </c>
       <c r="T50">
         <v>26927.5</v>
@@ -3174,33 +2815,9 @@
       <c r="H51">
         <v>3533</v>
       </c>
-      <c r="I51">
-        <v>156.407</v>
-      </c>
-      <c r="K51">
-        <v>0.172</v>
-      </c>
-      <c r="L51">
-        <v>0.584</v>
-      </c>
-      <c r="M51">
-        <v>0.57</v>
-      </c>
       <c r="N51">
         <v>1247</v>
       </c>
-      <c r="O51">
-        <v>173.5</v>
-      </c>
-      <c r="Q51">
-        <v>0.184</v>
-      </c>
-      <c r="R51">
-        <v>0.72</v>
-      </c>
-      <c r="S51">
-        <v>1.39</v>
-      </c>
       <c r="T51">
         <v>21933.4</v>
       </c>
@@ -3212,6 +2829,683 @@
       </c>
       <c r="Y51">
         <v>1.046</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1.955971877114539</v>
+      </c>
+      <c r="C2">
+        <v>0.5998240926222573</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>1.960152185520972</v>
+      </c>
+      <c r="C3">
+        <v>0.6020268364652204</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1.968579687268341</v>
+      </c>
+      <c r="C4">
+        <v>0.6037781070002887</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1.976739649277698</v>
+      </c>
+      <c r="C5">
+        <v>0.6043544321859223</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1.988399922859375</v>
+      </c>
+      <c r="C6">
+        <v>0.6028695866399573</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>1.987051076680233</v>
+      </c>
+      <c r="C7">
+        <v>0.5985499346199765</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1.95652925156873</v>
+      </c>
+      <c r="C8">
+        <v>0.5922270788116331</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1.897235757131885</v>
+      </c>
+      <c r="C9">
+        <v>0.5860301896299368</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1.851386134530128</v>
+      </c>
+      <c r="C10">
+        <v>0.5811665401426656</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1.794266400464627</v>
+      </c>
+      <c r="C11">
+        <v>0.5757823029151798</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1.739521081573981</v>
+      </c>
+      <c r="C12">
+        <v>0.5695798399889417</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>1.685400022072028</v>
+      </c>
+      <c r="C13">
+        <v>0.5625156761565241</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1.654844754493274</v>
+      </c>
+      <c r="C14">
+        <v>0.5515420879024104</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>1.611525611913544</v>
+      </c>
+      <c r="C15">
+        <v>0.5358876689820001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>1.549567867585666</v>
+      </c>
+      <c r="C16">
+        <v>0.5165412016770282</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>1.466396451531275</v>
+      </c>
+      <c r="C17">
+        <v>0.4951636618609842</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>1.383782409931075</v>
+      </c>
+      <c r="C18">
+        <v>0.4723324894684097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1.304735564837698</v>
+      </c>
+      <c r="C19">
+        <v>0.4490442700233985</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1.212623862538083</v>
+      </c>
+      <c r="C20">
+        <v>0.4272509288645279</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1.124737058601235</v>
+      </c>
+      <c r="C21">
+        <v>0.4098039936994392</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1.073207790311271</v>
+      </c>
+      <c r="C22">
+        <v>0.3971359871045846</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.059540968694506</v>
+      </c>
+      <c r="C23">
+        <v>0.3905478210560462</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1.079604219547568</v>
+      </c>
+      <c r="C24">
+        <v>0.3920137158705687</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1.103136569003515</v>
+      </c>
+      <c r="C25">
+        <v>0.4008336092336882</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1.125851807509618</v>
+      </c>
+      <c r="C26">
+        <v>0.4138404994966908</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1.141079277598117</v>
+      </c>
+      <c r="C27">
+        <v>0.4298025891158146</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1.176896160024435</v>
+      </c>
+      <c r="C28">
+        <v>0.4490286635386812</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1.224395611010598</v>
+      </c>
+      <c r="C29">
+        <v>0.4723135387369672</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1.291358577937113</v>
+      </c>
+      <c r="C30">
+        <v>0.4973318484877874</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1.349448143552905</v>
+      </c>
+      <c r="C31">
+        <v>0.5204428228563657</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>1.389556809276494</v>
+      </c>
+      <c r="C32">
+        <v>0.5396354548119808</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>1.434748730022306</v>
+      </c>
+      <c r="C33">
+        <v>0.5556700031101495</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1.469495453496577</v>
+      </c>
+      <c r="C34">
+        <v>0.5706711791702478</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>1.499850066271823</v>
+      </c>
+      <c r="C35">
+        <v>0.5829300729157261</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>1.519068337452331</v>
+      </c>
+      <c r="C36">
+        <v>0.5911859033312041</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1.52460863952699</v>
+      </c>
+      <c r="C37">
+        <v>0.5945613630257852</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>1.510328706010615</v>
+      </c>
+      <c r="C38">
+        <v>0.5914868855364673</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>1.472037081007688</v>
+      </c>
+      <c r="C39">
+        <v>0.5827550573371101</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1.435640529149012</v>
+      </c>
+      <c r="C40">
+        <v>0.5726855304476943</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1.414817019540433</v>
+      </c>
+      <c r="C41">
+        <v>0.565703858034497</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1.40591017576246</v>
+      </c>
+      <c r="C42">
+        <v>0.5611735184708321</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1.399845941700862</v>
+      </c>
+      <c r="C43">
+        <v>0.5584557606321964</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1.390537788315871</v>
+      </c>
+      <c r="C44">
+        <v>0.5590432333069137</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.404795426854078</v>
+      </c>
+      <c r="C45">
+        <v>0.5634699012220993</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1.434559222707881</v>
+      </c>
+      <c r="C46">
+        <v>0.5762805956772267</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1.493518292472212</v>
+      </c>
+      <c r="C47">
+        <v>0.5951677864319451</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.542767899244535</v>
+      </c>
+      <c r="C48">
+        <v>0.6108311233436224</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.568340239202821</v>
+      </c>
+      <c r="C49">
+        <v>0.6175608625035254</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_2019</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1.568117289421144</v>
+      </c>
+      <c r="C50">
+        <v>0.6145042209967416</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_2020</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1.533058436252526</v>
+      </c>
+      <c r="C51">
+        <v>0.6038583689216922</v>
       </c>
     </row>
   </sheetData>
